--- a/src/attributions/attributions_ig_traj_325.xlsx
+++ b/src/attributions/attributions_ig_traj_325.xlsx
@@ -2140,22 +2140,22 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01567133554034191</v>
+        <v>0.02443649297534976</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.001923071656116909</v>
+        <v>0.005518262783870211</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.003781889988198994</v>
+        <v>-0.007244598177466519</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2164,37 +2164,37 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.01004181118194705</v>
+        <v>-0.03986564912988261</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004802586507897447</v>
+        <v>-0.007390811570606851</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02016085629469601</v>
+        <v>0.02967144486556825</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>8.563474270963713e-05</v>
+        <v>0.004702654460457158</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
@@ -2203,52 +2203,52 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002314363373062915</v>
+        <v>0.0162593818445757</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.003831953146478992</v>
+        <v>0.006472913963661992</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.001925202140556881</v>
+        <v>-0.03148403328432695</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.01855547136036008</v>
+        <v>-0.05337311375037053</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.001496114359279056</v>
+        <v>-0.02757023715345557</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.007388931643596523</v>
+        <v>0.009966758082893441</v>
       </c>
       <c r="AM4" t="n">
         <v>-0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.007114524319546874</v>
+        <v>-0.03511145251713402</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.008563884211636596</v>
+        <v>-0.03248412850297028</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2272,22 +2272,22 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0381280886436914</v>
+        <v>0.1960945034222685</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.003423246677218751</v>
+        <v>-0.03065445961294668</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.02445662515755756</v>
+        <v>-0.03022627570625466</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,67 +2296,67 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.001767636948338929</v>
+        <v>0.003037716850126085</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.003065386335831319</v>
+        <v>0.003853514192197087</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.01072694673503197</v>
+        <v>0.02631650955039692</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.01071318448243143</v>
+        <v>0.02850649188080952</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.002611913106350454</v>
+        <v>0.06928729794422632</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01178212770631952</v>
+        <v>0.05735989544132958</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02154858176304079</v>
+        <v>0.056539617953324</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,25 +2365,25 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.005402754247061898</v>
+        <v>-0.03840147000541128</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004048552389359114</v>
+        <v>-0.05802906527973541</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.00531129539156331</v>
+        <v>-0.02576153048832303</v>
       </c>
       <c r="CF4" t="n">
         <v>-0</v>
@@ -2392,25 +2392,25 @@
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.004380637227858581</v>
+        <v>-0.006566237074603796</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.01815347828982091</v>
+        <v>0.03810982459261323</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.002382849158374006</v>
+        <v>-0.03534498762773063</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
@@ -2419,13 +2419,13 @@
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.004669053760966022</v>
+        <v>0.05158358190971555</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.004393895544164912</v>
+        <v>0.03805917987300861</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
         <v>-0</v>
@@ -2434,10 +2434,10 @@
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.00451463297957393</v>
+        <v>-0.02877984041214554</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
@@ -2446,13 +2446,13 @@
         <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.0031842618206526</v>
+        <v>-0.01584771174550989</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.02088614681632609</v>
+        <v>0.03730908064476736</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
@@ -2461,22 +2461,22 @@
         <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.003879558910977762</v>
+        <v>-0.008480799508075591</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01195797485953135</v>
+        <v>-0.02631907516917036</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.02751300694902171</v>
+        <v>0.01979724135769931</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,28 +2485,28 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.00234416344014678</v>
+        <v>-0.009755138058344959</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.003332899130554785</v>
+        <v>0.01537762732039345</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.001180617071687457</v>
+        <v>0.06770989004083713</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.002539280637874579</v>
+        <v>0.03709496685200665</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.0128544596443282</v>
+        <v>-0.03136374710566869</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.01103702261258085</v>
+        <v>-0.03610555772970597</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2539,52 +2539,52 @@
         <v>-0</v>
       </c>
       <c r="EE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.001740848360306624</v>
+        <v>-0.02222961810683983</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.004428173104733716</v>
+        <v>-0.03615373543578861</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01232050330052321</v>
+        <v>-0.009307818592650983</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.002989631924077858</v>
+        <v>0.01234721984535505</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.003281064492046538</v>
+        <v>-0.03074456573256625</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.02165518972387424</v>
+        <v>0.04292315020183476</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
@@ -2596,10 +2596,10 @@
         <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.003819851846447142</v>
+        <v>-0.03328510521706013</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,25 +2608,25 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.001749372237467405</v>
+        <v>-0.02121395838190572</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.02058749816374739</v>
+        <v>0.02970971913513441</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.006726413533409721</v>
+        <v>-0.02285733119749671</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01775905464494929</v>
+        <v>-0.007958046178564481</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.006921571076786827</v>
+        <v>-0.0165966876085666</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-7.11097487902253e-05</v>
+        <v>0.01450097366102765</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.009876234654456468</v>
+        <v>0.01866796429977616</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.01238895350150914</v>
+        <v>-0.005011544437624666</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,13 +2674,13 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
         <v>-0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01208131197626932</v>
+        <v>-0.008267394665288579</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2689,10 +2689,10 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.00716081340724323</v>
+        <v>0.02001375023043522</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,43 +2709,43 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04699081468772019</v>
+        <v>0.09565223750461942</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.002997590100996915</v>
+        <v>-0.01048136463941336</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002069622972569749</v>
+        <v>-0.02419731907179934</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.020003007359693</v>
+        <v>-0.06579331984909641</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03759284088554038</v>
+        <v>0.162007629949512</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01654585240231399</v>
+        <v>0.03299235732388645</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,109 +2760,109 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.420420385000164e-11</v>
+        <v>2.396964132463768e-11</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-9.778173818582533e-12</v>
+        <v>7.411752473217185e-12</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.00692438377747096</v>
+        <v>-0.002618991746464301</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01855315072767676</v>
+        <v>-0.01000277486390982</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.03709364531184377</v>
+        <v>-0.05682545226011675</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.06319437378501519</v>
+        <v>-0.03270936890200791</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.02130474254233649</v>
+        <v>0.07846223408797297</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.03770794449054438</v>
+        <v>-0.01076209976082027</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.04187378225878747</v>
+        <v>0.05591282307334085</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.2297617498757233</v>
+        <v>0.259861294074765</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.03454027881377188</v>
+        <v>-0.1351521468213816</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.199722015131381</v>
+        <v>-0.1116299520400425</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
@@ -2871,16 +2871,16 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1.379130063787356e-11</v>
+        <v>-5.738407191011656e-12</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-1.346138455662859e-11</v>
+        <v>1.270632150724429e-12</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.003135423494221905</v>
+        <v>0.000732661800947462</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2895,19 +2895,19 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0355750756936457</v>
+        <v>-0.02298742904802043</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.02024133802300544</v>
+        <v>0.04690808047580525</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1437089298999224</v>
+        <v>0.08095920666724969</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
@@ -2925,52 +2925,52 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1119369273402302</v>
+        <v>0.1832690134886348</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.01454544541979261</v>
+        <v>-0.09165298256364533</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.06463736847853091</v>
+        <v>0.004648172827060365</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.02739084328549814</v>
+        <v>-0.1004958867493421</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.0001067326442797787</v>
+        <v>0.06528671133843478</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.00254104807137837</v>
+        <v>0.01415715288890189</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,16 +2979,16 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.008689434859527187</v>
+        <v>-0.08627029712795463</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.03057745885717111</v>
+        <v>0.03426132953240872</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1093678907689475</v>
+        <v>-0.01229032802126768</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
@@ -3003,22 +3003,22 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.02013228090595248</v>
+        <v>-0.1070472230494224</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.009480297304456028</v>
+        <v>0.07340852854966261</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.02350664378425718</v>
+        <v>0.01732778368449064</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
         <v>0</v>
@@ -3030,106 +3030,106 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.001421924955394921</v>
+        <v>-0.005187750404518281</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.006134067265923841</v>
+        <v>0.03558177133118123</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.0365505764425074</v>
+        <v>-0.04395067704635645</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.06079445534525916</v>
+        <v>-0.04365080004567454</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.002309127397519384</v>
+        <v>0.009516244797967933</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02338387715156645</v>
+        <v>-0.05822905806438444</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.00234543643234427</v>
+        <v>0.06131073451496542</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.03765184245687143</v>
+        <v>0.04195143380830228</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.007739870375797994</v>
+        <v>-0.01984623131550882</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.03289883792630299</v>
+        <v>-0.05873776344025645</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.001513989586684792</v>
+        <v>0.07895580968935144</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.04199218992434518</v>
+        <v>0.03397220862890962</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3141,49 +3141,49 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.05297258736036116</v>
+        <v>-0.05947768303069692</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.01650090154753673</v>
+        <v>0.04995650294941213</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.005165857609731369</v>
+        <v>-0.04327422300462296</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.02687109973777594</v>
+        <v>-0.1173966349874334</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.01081689696011484</v>
+        <v>0.08177585501049858</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01867201436678137</v>
+        <v>0.006613588181552795</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,46 +3192,46 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.05294282267279215</v>
+        <v>-0.05644891799283961</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.02500328724624444</v>
+        <v>-0.0270183513913479</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0200570803300811</v>
+        <v>0.06970228516458284</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.09614085955530258</v>
+        <v>0.03465306667880969</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.008226696544721634</v>
+        <v>0.1200678597001215</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.04712583556629776</v>
+        <v>-0.06459743513301956</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
@@ -3240,28 +3240,28 @@
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.004333389569294627</v>
+        <v>-0.07679032672548017</v>
       </c>
       <c r="GA5" t="n">
         <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.02076683999386933</v>
+        <v>0.01031234202958327</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3278,22 +3278,22 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.008842821717074614</v>
+        <v>0.01930469642152029</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.005883301219412199</v>
+        <v>0.005447874744748566</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001925379299636266</v>
+        <v>0.006320853619883309</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -3305,25 +3305,25 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0004544061064929843</v>
+        <v>-0.006441875044788443</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003642368703969727</v>
+        <v>-0.002113205282588098</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008281390904500974</v>
+        <v>0.02119460386258518</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.000854439783653198</v>
+        <v>-0.001178658033962778</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-3.618543321689733e-12</v>
+        <v>-1.323870201415589e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.002820482287762086</v>
+        <v>0.0008241325041253389</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.007733383764855877</v>
+        <v>-0.0101204340062043</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01014196223500756</v>
+        <v>-0.04525235741624564</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.003007801919625755</v>
+        <v>-0.01572548493134538</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.005154377127610871</v>
+        <v>0.01063280771438195</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.008913149725295071</v>
+        <v>-0.009182702422131556</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.004799551913304139</v>
+        <v>-0.02503207694978414</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3413,19 +3413,19 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.03080344409218742</v>
+        <v>0.0964588953016278</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0002367360710078313</v>
+        <v>-0.01741481565360528</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.008065301682119276</v>
+        <v>-0.02106580182941637</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3437,25 +3437,25 @@
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0001459465860564515</v>
+        <v>-0.0007062281421991798</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-8.230895979045684e-12</v>
+        <v>-4.761263398761462e-12</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.00102143577629904</v>
+        <v>0.01756336383105573</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,37 +3464,37 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.01385857860127242</v>
+        <v>0.01460252906402163</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.004493595591612471</v>
+        <v>0.04173867372372989</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.006137606315772108</v>
+        <v>0.03423487854456243</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.00952839559495427</v>
+        <v>0.03278687776698952</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.006470761186687291</v>
+        <v>-0.004407618020408585</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01409538689247348</v>
+        <v>-0.03108957700905953</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.001188917179223235</v>
+        <v>-0.01277812639028693</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
         <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.002280838963741892</v>
+        <v>0.0006288996881652903</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.004871080067014735</v>
+        <v>0.02009436678812116</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3545,76 +3545,76 @@
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.01037174974151326</v>
+        <v>-0.0244795286502081</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.00685226900462015</v>
+        <v>0.03511934934238812</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.0132225789527203</v>
+        <v>0.02310459152772368</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.001988163943751263</v>
+        <v>-0.01419752137508764</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.00142952234091388</v>
+        <v>-0.001541673850235624</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.007313834898204941</v>
+        <v>0.01845868410182753</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.008065633840391566</v>
+        <v>-0.007085688348018799</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0005748443835765168</v>
+        <v>-0.0006155975007869841</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01406448771527862</v>
+        <v>-0.003096421636521819</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,31 +3623,31 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.004476118811896428</v>
+        <v>-0.01078081663952022</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01124977926837143</v>
+        <v>-0.003169570866533859</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.004982065315320153</v>
+        <v>0.03362391336163729</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,49 +3656,49 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01583570803685504</v>
+        <v>0.01083498376473817</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.008254421324915549</v>
+        <v>-0.01705424887676698</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.008845630496145233</v>
+        <v>0.01766461845005624</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.002616734144041544</v>
+        <v>-0.003096221272967801</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.002299873588602382</v>
+        <v>-0.01054226755472253</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.003031294663312062</v>
+        <v>-0.0008831999778742646</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM6" t="n">
         <v>0</v>
@@ -3707,37 +3707,37 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.002133739210039284</v>
+        <v>0.0004431380498460566</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.004454740022581529</v>
+        <v>-0.0184320020067267</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.01833915346310076</v>
+        <v>0.01944612574476785</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.004232652972958858</v>
+        <v>-0.01696927803826482</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,16 +3746,16 @@
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.001477976724755129</v>
+        <v>-0.007225197664922869</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.006974468242123499</v>
+        <v>0.01455820985842238</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
@@ -3764,19 +3764,19 @@
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01442014799003476</v>
+        <v>-0.009883989715182142</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01118603640064535</v>
+        <v>0.01252083327977201</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.003702517804954172</v>
+        <v>0.006813683576106628</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,25 +3785,25 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.001611569162308054</v>
+        <v>0.01384319558957114</v>
       </c>
       <c r="FR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.0004422874538171849</v>
+        <v>-0.0001167698792604669</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.005906549730056589</v>
+        <v>-0.03621135826372197</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,25 +3812,25 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.003285904625199676</v>
+        <v>0.003048284184096549</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.00260262844700737</v>
+        <v>0.008896465584089495</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03919468074931017</v>
+        <v>0.03084489060021621</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01547986419447986</v>
+        <v>-0.003385088753771394</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,13 +3868,13 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009210267402255097</v>
+        <v>0.003837567400245186</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.00219520691896103</v>
+        <v>-0.00415688697432781</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0002902132623002688</v>
+        <v>0.001329493951429654</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,52 +3892,52 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02686048953818593</v>
+        <v>0.001142904787455136</v>
       </c>
       <c r="S7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0017045605693939</v>
+        <v>-0.002128457378177222</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0006450896043324879</v>
+        <v>-0.003460301479453056</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
         <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0006482504858728567</v>
+        <v>0.000624080503279937</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01725170151535363</v>
+        <v>-0.01436248071531152</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0149555010023618</v>
+        <v>-0.01506790474159023</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0180144010494598</v>
+        <v>0.0006672757083480097</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01571482056737866</v>
+        <v>0.02491491006185038</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01378582864115066</v>
+        <v>-0.002144806333229222</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01464339083816128</v>
+        <v>-0.01261169943814565</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1318926999934933</v>
+        <v>0.100590059857697</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.07881906676914228</v>
+        <v>-0.01915867826216227</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.001587449560533985</v>
+        <v>0.0129386872701549</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.001760777744056896</v>
+        <v>-0.001097704466461575</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,25 +4018,25 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.002314197789616046</v>
+        <v>-0.001371108733307421</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.02896324037906408</v>
+        <v>0.02395714762875439</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0005080843210352728</v>
+        <v>0.01746221244323018</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
@@ -4045,52 +4045,52 @@
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.04226170535306503</v>
+        <v>0.03806157675618494</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02607047399336422</v>
+        <v>0.01236015409810282</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0478393792267295</v>
+        <v>0.04916254991336483</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.02649933213642525</v>
+        <v>-0.0164145100822003</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.01268734059029185</v>
+        <v>-0.01406726635399896</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.01390634455742007</v>
+        <v>-0.0202022677640853</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,7 +4099,7 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.007393818278409464</v>
+        <v>-0.003219691651850837</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
@@ -4111,22 +4111,22 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.01744220821586703</v>
+        <v>0.01016739421974043</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.005069944978896601</v>
+        <v>-0.0316569078886774</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.004299834234916242</v>
+        <v>0.00353312513416043</v>
       </c>
       <c r="CR7" t="n">
         <v>-0</v>
@@ -4138,22 +4138,22 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.002610799543212085</v>
+        <v>0.02891476091223247</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01185769174042145</v>
+        <v>-0.02095673029624973</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.004860737341540623</v>
+        <v>-0.002956123419399684</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
@@ -4165,148 +4165,148 @@
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.01772398236214692</v>
+        <v>0.008303122440720311</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.03224759629648891</v>
+        <v>-0.009689961672314456</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03360032483698504</v>
+        <v>-0.01305470345199164</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0032341904447024</v>
+        <v>-0.001490206849197601</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0009499992191781636</v>
+        <v>-0.02013001606726236</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.003451901895626702</v>
+        <v>0.001168935273081138</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.007235803824694889</v>
+        <v>-0.02402915862546311</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.007709472411541623</v>
+        <v>0.015053639451441</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.00407705085837197</v>
+        <v>-0.005481959748135563</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.01024856545326061</v>
+        <v>-0.002292700565617119</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.004215743433920147</v>
+        <v>-0.01730816527639912</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
         <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.001440960362568181</v>
+        <v>-0.01012028422567201</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.02470757216789808</v>
+        <v>0.00398068717098214</v>
       </c>
       <c r="EO7" t="n">
         <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.0422057010959366</v>
+        <v>0.005499614579380603</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.00262565850687477</v>
+        <v>-0.00328899531747761</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.009939383187204701</v>
+        <v>0.00684801262293712</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.01910132180486955</v>
+        <v>-0.02422921088327266</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.002676790601548233</v>
+        <v>-0.01032026211179874</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,49 +4327,49 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01143680882526962</v>
+        <v>0.009993728353990807</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.004092917541881958</v>
+        <v>-0.01220821425386241</v>
       </c>
       <c r="FI7" t="n">
         <v>0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01707909593968408</v>
+        <v>-0.003442649454486574</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.005442860281002179</v>
+        <v>0.03799451652890638</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.03732099111666496</v>
+        <v>0.007350992400376373</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01653156573766042</v>
+        <v>-0.009699116184481642</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
@@ -4378,19 +4378,19 @@
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0006235150334268566</v>
+        <v>0.001701595315279085</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03334894539099834</v>
+        <v>-0.00849549197244286</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.01434756470511656</v>
+        <v>-0.0005457799456035636</v>
       </c>
     </row>
     <row r="8">
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2496662987834158</v>
+        <v>0.1812321995193031</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1003615423477135</v>
+        <v>-0.1265136602219386</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.005288236973213054</v>
+        <v>0.0793985715558401</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5012,43 +5012,43 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01273280390469787</v>
+        <v>0.01417371439535675</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05615744433080609</v>
+        <v>0.09906983758372348</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0007788682065893336</v>
+        <v>-0.001423567593868899</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0159452625302905</v>
+        <v>0.0353420506910867</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.01437653128287097</v>
+        <v>-0.004472630371546473</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01734701299389794</v>
+        <v>-0.003255427456324032</v>
       </c>
       <c r="X9" t="n">
         <v>-0</v>
@@ -5057,7 +5057,7 @@
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,43 +5066,43 @@
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.07820423440874827</v>
+        <v>0.03255056919707309</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.004615013793487137</v>
+        <v>-0.07783358841629889</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.03470274265326472</v>
+        <v>-0.1654110790303226</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.06537130652677167</v>
+        <v>0.158469386248913</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.06420466417008622</v>
+        <v>-0.1131268860166304</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.09192680736985287</v>
+        <v>0.1177566795678505</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,52 +5111,52 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4845478253752625</v>
+        <v>0.3390439277709584</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.06288966802730714</v>
+        <v>-0.2480683530365116</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1941068278289766</v>
+        <v>-0.1291060202248058</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.006880014131239389</v>
+        <v>-0.0103527855722659</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.006758338516098154</v>
+        <v>0.002847924313178938</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.01885676104710685</v>
+        <v>0.00652392266849596</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,31 +5165,31 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.04373648070606284</v>
+        <v>0.02946948528928751</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.04845785738788445</v>
+        <v>0.05284398523598167</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1138329199514016</v>
+        <v>-0.02392821010435692</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2472530556075988</v>
+        <v>0.2650889420081063</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.07997965590366114</v>
+        <v>-0.2794091087391373</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.02746492935523543</v>
+        <v>0.06765113893257366</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>-0</v>
@@ -5228,130 +5228,130 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.08093070669787564</v>
+        <v>-0.08887574225001744</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.03027383997515347</v>
+        <v>0.1984999674356797</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.03017411977009676</v>
+        <v>-0.100273785927783</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.05656024621151123</v>
+        <v>-0.1291288883806562</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1216791586154462</v>
+        <v>0.2323012492360914</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1796305460432978</v>
+        <v>-0.006356251944424144</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.0804752561047216</v>
+        <v>-0.1004287727635244</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.06331746451548649</v>
+        <v>0.1958299833984683</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.004417027553799506</v>
+        <v>-0.08306822129314238</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01166402768660995</v>
+        <v>-0.01797920032932421</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.06359612793841739</v>
+        <v>0.08956833375755435</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.05382924665225017</v>
+        <v>-0.1252888252863736</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.05094885539223424</v>
+        <v>-0.08267718391803684</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.01263402601765664</v>
+        <v>0.07703588828609005</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.03429267319327076</v>
+        <v>-0.09939370869423499</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5360,52 +5360,52 @@
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0456530920674928</v>
+        <v>0.03351273282322693</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.04706618842161064</v>
+        <v>0.07419561430855651</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.009888167829144883</v>
+        <v>-0.04650614008429329</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.03048769131324683</v>
+        <v>-0.00696170826174055</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.062609859092931</v>
+        <v>0.17842466261109</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.015365191815184</v>
+        <v>-0.05698144136240119</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5414,28 +5414,28 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.09585586915928634</v>
+        <v>-0.07001146982888933</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.07628789869352054</v>
+        <v>-0.17036352065722</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.07668287521740445</v>
+        <v>-0.08197086918395248</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
         <v>-0</v>
@@ -5444,43 +5444,43 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.08628527956258754</v>
+        <v>-0.1147671248057587</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.05262514034641411</v>
+        <v>0.2231361539365033</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.02378939893446546</v>
+        <v>-0.09345013001051268</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.001891045609774924</v>
+        <v>-0.03900464334623726</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04118545316800837</v>
+        <v>0.05963927254503608</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0536594239929019</v>
+        <v>-0.08959585150912773</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5492,28 +5492,28 @@
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.04757545541819704</v>
+        <v>0.02860210089095343</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.008791926860107926</v>
+        <v>0.1736119289712142</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.06501622239565893</v>
+        <v>-0.04446685007817731</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
@@ -5522,31 +5522,31 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.03816996224628663</v>
+        <v>-0.05960278387420351</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.01331582104559085</v>
+        <v>0.1563856821367013</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1299859523310019</v>
+        <v>0.131666333322253</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.02940221668283416</v>
+        <v>-0.04357958207268802</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.04137914807006387</v>
+        <v>-0.03456681947765893</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0005796213257499482</v>
+        <v>-0.005477593100032079</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,16 +5581,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02473438098828509</v>
+        <v>0.03228147136287386</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02974517772818213</v>
+        <v>0.05233941806509995</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.004831968555983041</v>
+        <v>-0.004027342101337834</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,7 +5599,7 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.01192302472268048</v>
+        <v>0.008370024143095747</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
@@ -5608,43 +5608,43 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.03563876976340338</v>
+        <v>0.03337379642373989</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.009068289392355712</v>
+        <v>-0.02030883535134177</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.001557508092338095</v>
+        <v>-0.02944575215523152</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.002274844033983848</v>
+        <v>0.007369294947304685</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.01594024658204436</v>
+        <v>-0.01004446600621062</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.06278396585439215</v>
+        <v>-0.07264839289007469</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.01325758240849093</v>
+        <v>-0.07379491889672767</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01270611205781918</v>
+        <v>0.01740811398448022</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -5662,16 +5662,16 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.01044871183951657</v>
+        <v>0.08802267590513924</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.03027375584694591</v>
+        <v>-0.01297412110029881</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.06488359956318754</v>
+        <v>0.042724652490898</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -5680,34 +5680,34 @@
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.004607216136237265</v>
+        <v>-0.01822197877752831</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2897292584345153</v>
+        <v>0.2153229068296278</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.04608358671053553</v>
+        <v>-0.04793774931041139</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.129943941306313</v>
+        <v>-0.1519088100446084</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.03989485887910153</v>
+        <v>-0.03477196985754659</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.00274145882222404</v>
+        <v>-0.002590703619840462</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.009628114584268006</v>
+        <v>-0.01653974070149705</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.05582740358318073</v>
+        <v>-0.002526024365478529</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.007922381404545925</v>
+        <v>-0.01751994942891587</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,25 +5743,25 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.09582919485546577</v>
+        <v>0.03613864746021042</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1017776293496123</v>
+        <v>0.0357047504605854</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.05621429304300584</v>
+        <v>0.05195891077127154</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.05405955028957849</v>
+        <v>0.01587429391652213</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,97 +5770,97 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1542170621213159</v>
+        <v>0.1508011012496254</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.02784005005144844</v>
+        <v>-0.05182686378498259</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.02197638297586751</v>
+        <v>-0.09425243261663137</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.01514588747280373</v>
+        <v>-0.0502677092756174</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.04711721478308185</v>
+        <v>-0.06694379604507626</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01367311833079761</v>
+        <v>0.05188647660821531</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01405360458545685</v>
+        <v>0.01112136603263673</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.01187751714603649</v>
+        <v>-0.005491958872937359</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.04945312653927172</v>
+        <v>-0.07153762970428929</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.07017153526788257</v>
+        <v>0.07928852774562083</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.03287123134753681</v>
+        <v>0.09563960919633285</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.04842079904828514</v>
+        <v>0.02006683570813825</v>
       </c>
       <c r="CU10" t="n">
         <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02806956239398626</v>
+        <v>-0.07066522332808647</v>
       </c>
       <c r="CX10" t="n">
         <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.03369932674717268</v>
+        <v>0.06160264919298494</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.01839254933341269</v>
+        <v>0.02340339734482618</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,34 +5869,34 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.01490839582406044</v>
+        <v>-0.008987586472411897</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.04654185973764197</v>
+        <v>-0.0544516824071089</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01855124102527658</v>
+        <v>0.02438397523967112</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.005762721834932603</v>
+        <v>-0.01445733989354715</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.007264052902888819</v>
+        <v>-0.008459766423528562</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
@@ -5905,70 +5905,70 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.07329776077411788</v>
+        <v>-0.06262190941767262</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.01102592315871934</v>
+        <v>0.03386766107397124</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.05577409620299251</v>
+        <v>-0.05707071871415709</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.05973494753121723</v>
+        <v>0.05626649737189451</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.02158476758015909</v>
+        <v>0.08118226020110293</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.01985554037821216</v>
+        <v>0.0682116115850752</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.01828009527514125</v>
+        <v>-0.03798153204754089</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.007163942619161775</v>
+        <v>0.07511966701198318</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02703318998370449</v>
+        <v>-0.02298330171708018</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.04926819972759348</v>
+        <v>0.0248122154555022</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.005039977760046984</v>
+        <v>-0.001947888161262651</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,106 +5977,106 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.07792886582258754</v>
+        <v>-0.02201427702097172</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.06962480090931868</v>
+        <v>-0.003999355536396325</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.04420912527980097</v>
+        <v>0.04523830009887849</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.07411415406786084</v>
+        <v>-0.004322490834745348</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.01999267047805387</v>
+        <v>0.002922579139684644</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.04544303651976302</v>
+        <v>-0.08597809563931263</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.03055265639138256</v>
+        <v>0.06716674268518059</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.001401414207885027</v>
+        <v>0.01106257880713301</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.005922891480010188</v>
+        <v>-0.003702887973770427</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.05300645436388881</v>
+        <v>-0.01190893605911458</v>
       </c>
       <c r="FI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.02600230782696497</v>
+        <v>0.005787431281608918</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.04156660549208569</v>
+        <v>0.04031122054409991</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.01954583202175084</v>
+        <v>-0.005979674516352942</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.0671931548172862</v>
+        <v>0.008872504594461421</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.03279686780219747</v>
+        <v>0.08941997955920655</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.02251160493409102</v>
+        <v>-0.1500360639297619</v>
       </c>
       <c r="FU10" t="n">
         <v>-0</v>
@@ -6085,34 +6085,34 @@
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.000957428261148275</v>
+        <v>0.0458909118055434</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.04472394309577911</v>
+        <v>-0.04329358643914936</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.02772620629182646</v>
+        <v>0.01311562561776401</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.01457096976144628</v>
+        <v>-0.02030258838669824</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,25 +6123,25 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.03192127769382491</v>
+        <v>0.3282765022464724</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.002167365275056068</v>
+        <v>0.04688595300174128</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.04521285125905532</v>
+        <v>-0.212833630126667</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.006559247809877196</v>
+        <v>0.1201171253069738</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,25 +6159,25 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.001678411740210573</v>
+        <v>-0.01299666956867715</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.00434144158194434</v>
+        <v>-0.02269212102712352</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.006187777515251562</v>
+        <v>0.1084764540008693</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,40 +6186,40 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.002109380022389783</v>
+        <v>-0.05641854982740856</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001956727998272055</v>
+        <v>0.007340775682566253</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" t="n">
         <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01090818566595523</v>
+        <v>-0.1510934216258602</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01728762133353848</v>
+        <v>-0.2446040903166794</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.00476903484194214</v>
+        <v>0.05387935427316615</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
@@ -6228,10 +6228,10 @@
         <v>-0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.0002124462788537997</v>
+        <v>0.1294772287423899</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,43 +6240,43 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.008133374310037961</v>
+        <v>0.06905747131326588</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.005911279271414144</v>
+        <v>-0.04846438666144737</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.0448942934773507</v>
+        <v>0.4716555296361973</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.006545144825219282</v>
+        <v>-0.2401265988337931</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.0123523625939461</v>
+        <v>-0.100420547432718</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB11" t="n">
         <v>0</v>
@@ -6285,52 +6285,52 @@
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.01004170634235087</v>
+        <v>0.023560872110441</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.007217207811560774</v>
+        <v>-0.0008599178239553521</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.02451868129229942</v>
+        <v>-0.06896306597515493</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.03312393375153382</v>
+        <v>0.05125532876635065</v>
       </c>
       <c r="BN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0132077058663768</v>
+        <v>0.09851822245669578</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0.0003798049843237398</v>
+        <v>0.120041184093289</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT11" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.008799870562731732</v>
+        <v>0.4245479936832323</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,43 +6348,43 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.004505915978035938</v>
+        <v>0.001552736869212203</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.004847558917821859</v>
+        <v>-0.0981627505836854</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.006277630277000806</v>
+        <v>-0.1615381970254513</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0009887771333671868</v>
+        <v>-0.05984525423610144</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.01715867296927413</v>
+        <v>0.12682820234121</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
         <v>-0</v>
@@ -6393,22 +6393,22 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0009310031713916565</v>
+        <v>-0.1783585471160043</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.009654355918047926</v>
+        <v>0.03142178695032172</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.00732665944015741</v>
+        <v>0.02402303912539432</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>0</v>
@@ -6420,22 +6420,22 @@
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.001724683164835119</v>
+        <v>-0.1382527761462963</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.002521822765494476</v>
+        <v>-0.04778921621761726</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.01553093123055343</v>
+        <v>0.1362112766089477</v>
       </c>
       <c r="DB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC11" t="n">
         <v>0</v>
@@ -6444,49 +6444,49 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.004851043593774697</v>
+        <v>-0.1634310873663916</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH11" t="n">
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.00958581348764566</v>
+        <v>-0.1553716097347533</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0114280054080177</v>
+        <v>0.09108448849597787</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.004061869758191452</v>
+        <v>-0.1081218605885379</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02140611915623683</v>
+        <v>0.04074601183651255</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.007521507763303464</v>
+        <v>0.03466663279584377</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6501,25 +6501,25 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.008140049058601013</v>
+        <v>0.02180429308596697</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.008523572928944484</v>
+        <v>0.03208913569974944</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.004120462242513867</v>
+        <v>0.1599006792127356</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
@@ -6528,19 +6528,19 @@
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.001196280578368076</v>
+        <v>0.01611472986412271</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
         <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.008022228321931675</v>
+        <v>-0.107759913101593</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.009987676074284231</v>
+        <v>0.05874335745969072</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6552,10 +6552,10 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.007600122381612946</v>
+        <v>-0.06946027257727681</v>
       </c>
       <c r="EQ11" t="n">
         <v>-0</v>
@@ -6564,16 +6564,16 @@
         <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.001654858908959142</v>
+        <v>-0.2938210612126899</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01375371802632202</v>
+        <v>0.07969576586454818</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
@@ -6582,22 +6582,22 @@
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.0009650320346089882</v>
+        <v>-0.1699494831445836</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.002647621003954301</v>
+        <v>-0.08804191935296612</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.01766570558997187</v>
+        <v>0.1079791632002424</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>-0</v>
@@ -6606,10 +6606,10 @@
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.003273546861829438</v>
+        <v>-0.1726010838064041</v>
       </c>
       <c r="FI11" t="n">
         <v>0</v>
@@ -6618,25 +6618,25 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.01844461567922705</v>
+        <v>0.131266374262836</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.006966312777965753</v>
+        <v>0.1179380116189638</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.003124908442826153</v>
+        <v>0.04678962282315974</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
@@ -6645,43 +6645,43 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.001648633314820085</v>
+        <v>-0.03304235230219994</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.02360035712904761</v>
+        <v>-0.05895583643394655</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.01997523112673393</v>
+        <v>-0.01822945266080258</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.002452396013568039</v>
+        <v>0.1371987065759436</v>
       </c>
       <c r="GE11" t="n">
         <v>0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
         <v>0</v>
@@ -6692,43 +6692,43 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1786855064131685</v>
+        <v>0.2072803562995653</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.09404937713504735</v>
+        <v>-0.1132313398094823</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0004866961718810459</v>
+        <v>-0.01893540739138403</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04623302011231223</v>
+        <v>0.07667612441732084</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01212222872717321</v>
+        <v>0.01971207900326096</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.004374545655461683</v>
+        <v>-0.01555544149356997</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6743,28 +6743,28 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03788838917472091</v>
+        <v>0.0551826003527795</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01291895784616135</v>
+        <v>-0.01086740747440287</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02974823766857936</v>
+        <v>-0.0221870024791371</v>
       </c>
       <c r="X12" t="n">
         <v>-0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,43 +6773,43 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03849612938329772</v>
+        <v>-0.04130642576518684</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.009085871771403166</v>
+        <v>-0.09900868117114114</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.005198937713703968</v>
+        <v>-0.07902089161137943</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02186071217890684</v>
+        <v>0.0976774637119036</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04064910678920006</v>
+        <v>-0.07118060459986275</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.04287241658473091</v>
+        <v>0.06632255555131453</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,31 +6818,31 @@
         <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2846046527907125</v>
+        <v>0.2528552194251835</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.01477066526463485</v>
+        <v>-0.1152057581272824</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1355640065061368</v>
+        <v>-0.1381283281474455</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
         <v>-0</v>
@@ -6854,16 +6854,16 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.005099538214369825</v>
+        <v>-0.001833253468769686</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.02181366450197863</v>
+        <v>-0.002327724005521558</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.03848436057374957</v>
+        <v>0.009340073029398228</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0683596626134816</v>
+        <v>0.003536373186714694</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.04361471875991176</v>
+        <v>0.05409796740428353</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.07954089695326336</v>
+        <v>0.08175085963247611</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,25 +6908,25 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1365737988685334</v>
+        <v>0.2270780733480276</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.02454381925620269</v>
+        <v>-0.1040979234363812</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.06315297373617226</v>
+        <v>-0.03088820828930457</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.04561318330148684</v>
+        <v>-0.08430023847970326</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01836937340616224</v>
+        <v>0.09957855140064399</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.02312977860730333</v>
+        <v>-0.008530517739970029</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6956,25 +6956,25 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.02625704034022857</v>
+        <v>-0.0832167329397261</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.09904436072858433</v>
+        <v>0.09394197904538043</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.09226866179803805</v>
+        <v>-0.00763595167033674</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,16 +6989,16 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.03828204939013863</v>
+        <v>-0.088820713066082</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.02781754453525</v>
+        <v>0.1019297963147829</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.0147256493600479</v>
+        <v>0.004521894470999521</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7010,28 +7010,28 @@
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.03518678049167209</v>
+        <v>-0.09523414979698987</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01670480755888969</v>
+        <v>0.02851185568960685</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.01399179554407953</v>
+        <v>-0.02135402418006967</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,214 +7043,214 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.04097273447392315</v>
+        <v>-0.07745061720886894</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.03402536907116584</v>
+        <v>0.03148597954391326</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01843879346187738</v>
+        <v>0.001865375683251342</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0279539008569438</v>
+        <v>0.02662681528011088</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.02108849109361009</v>
+        <v>-0.09780609060072142</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.009021710356036571</v>
+        <v>0.06096564681095101</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.01935939362592573</v>
+        <v>-0.02009228234550435</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.02419663762447629</v>
+        <v>0.06455178137788703</v>
       </c>
       <c r="EJ12" t="n">
-        <v>5.610298257030234e-05</v>
+        <v>0.01226643520037811</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.06285643367160533</v>
+        <v>-0.04544320857562613</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0.00140029512026229</v>
+        <v>0.08005939485909183</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02176613964548681</v>
+        <v>-0.03823316159235294</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.04157068286013278</v>
+        <v>-0.1050877501690738</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.02431491926729434</v>
+        <v>0.1109081424652029</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.01550907401484989</v>
+        <v>-0.01234337307787906</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01835015660977493</v>
+        <v>-0.06429735955251424</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.04059958159768784</v>
+        <v>0.008455297139893255</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.003567163735715632</v>
+        <v>0.05502828232761914</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
         <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01956596056434734</v>
+        <v>-0.0270541522598121</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.006726939796592385</v>
+        <v>0.1278736154232149</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0558540920820175</v>
+        <v>-0.005514161072732818</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.03936570386150628</v>
+        <v>-0.05754290497178073</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.04686902614062403</v>
+        <v>0.03768901595031929</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.09210470742889779</v>
+        <v>0.3333843544733356</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01347309578128683</v>
+        <v>0.05911011980484893</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1174093184459797</v>
+        <v>-0.2910017092167267</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7285,10 +7285,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02851388526764089</v>
+        <v>0.1842200933909829</v>
       </c>
       <c r="L13" t="n">
         <v>-0</v>
@@ -7297,16 +7297,16 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.003202288833256647</v>
+        <v>-0.01351390223201413</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0290507492276012</v>
+        <v>-0.08004787515426101</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,61 +7315,61 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.007126248783668201</v>
+        <v>0.1437260623844258</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.02732653118966045</v>
+        <v>-0.1267960448015014</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.0009183027925723772</v>
+        <v>0.02415409956026806</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0202770066918281</v>
+        <v>-0.06757515216665978</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.03225104004230271</v>
+        <v>-0.3490005660986713</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.005288528062354792</v>
+        <v>-0.131785759562717</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.02298562850916325</v>
+        <v>0.1801915509764161</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.007578445753080643</v>
+        <v>0.1064173938916511</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.0266501480552579</v>
+        <v>-0.1988540206962776</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,22 +7393,22 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1066602616663326</v>
+        <v>0.7581730163328849</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.03028376030774575</v>
+        <v>-0.240519048912271</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.07082374029344093</v>
+        <v>-0.1857609832285469</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -7417,13 +7417,13 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0227608417246574</v>
+        <v>-0.06775821283324417</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,91 +7432,91 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.01226777839459723</v>
+        <v>-0.1470369149392562</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.0311657199056336</v>
+        <v>-0.1375329777232686</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.04739430713255471</v>
+        <v>0.05868968412822191</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.002702328582188806</v>
+        <v>0.1195583005612086</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01244879839145795</v>
+        <v>0.06732986898746859</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.04805344107747205</v>
+        <v>0.4635233265868829</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.03251924546652708</v>
+        <v>-0.05599758331957543</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.03093609677553102</v>
+        <v>-0.2266556571273781</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.01783943910342767</v>
+        <v>-0.1836728462335205</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.007980343735665554</v>
+        <v>0.0003437714047571639</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.04149341551779026</v>
+        <v>0.1777795199547939</v>
       </c>
       <c r="CJ13" t="n">
         <v>-0</v>
@@ -7525,25 +7525,25 @@
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.0003697603242616283</v>
+        <v>-0.3162721068273555</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01080122900923652</v>
+        <v>0.4789604669790899</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.02319427071718367</v>
+        <v>0.3164923740524153</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7555,22 +7555,22 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.01112362524141081</v>
+        <v>-0.1622914437877174</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.004628190334300436</v>
+        <v>-0.02804688918665574</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0431654212000912</v>
+        <v>0.1538888975590849</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7585,46 +7585,46 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.009714807367917787</v>
+        <v>-0.02617588073103629</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01741122598315361</v>
+        <v>-0.14484298163632</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.002990208032855752</v>
+        <v>0.02556868180146237</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.008028022663026995</v>
+        <v>-0.06734458062803089</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.02972949716014356</v>
+        <v>-0.05255107562599397</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.004252059201653312</v>
+        <v>0.1572456348259931</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7639,25 +7639,25 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01265400618242716</v>
+        <v>0.06877025755220999</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01476516189036527</v>
+        <v>-0.03461893278483121</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01054565357211986</v>
+        <v>0.08618488514867551</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
@@ -7666,19 +7666,19 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.005633143947147426</v>
+        <v>-0.05171685838307127</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.001066540610547093</v>
+        <v>-0.07552267781221189</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.04277678075998081</v>
+        <v>-0.007883499908709096</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7687,13 +7687,13 @@
         <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.009695984453779458</v>
+        <v>-0.044442950691788</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,37 +7702,37 @@
         <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.0231305366115153</v>
+        <v>-0.1769428251941141</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.06209071167172104</v>
+        <v>0.09684121211331802</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.01060744151932904</v>
+        <v>-0.194269251137249</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.006460767158145609</v>
+        <v>-0.05909717515547016</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.04328426184087002</v>
+        <v>0.148741981713384</v>
       </c>
       <c r="FD13" t="n">
         <v>-0</v>
@@ -7747,19 +7747,19 @@
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.02761044702433122</v>
+        <v>-0.1796166302837107</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.0005993825475118104</v>
+        <v>0.164688729881947</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.007172516400954189</v>
+        <v>-0.08926223097470794</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
@@ -7774,34 +7774,34 @@
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0009129268856865214</v>
+        <v>0.0486330243473996</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0009157080170955358</v>
+        <v>0.01269122189506395</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.009167428614215803</v>
+        <v>-0.004195265694135939</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.01239751276556495</v>
+        <v>-0.07968524517550477</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
@@ -7810,16 +7810,16 @@
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.01261081818820498</v>
+        <v>0.02101204961789779</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7830,73 +7830,73 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3017656482574297</v>
+        <v>0.2183539451476497</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.07990930653393963</v>
+        <v>-0.08784651724961051</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.02654266565282948</v>
+        <v>-0.02669976072399244</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08347348576049204</v>
+        <v>0.09256368865195201</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.006227333897861984</v>
+        <v>-0.008366293393501024</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01555403073214295</v>
+        <v>-0.02519800934203897</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.09093443021960643</v>
+        <v>0.03597822020275677</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.01874267695440963</v>
+        <v>-0.0191633078859368</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01589974757612766</v>
+        <v>-0.04848238453132938</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
@@ -7908,55 +7908,55 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.03869440976836925</v>
+        <v>-0.02364616462448322</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.01592635975434656</v>
+        <v>-0.06672735274123018</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.02295562794138831</v>
+        <v>-0.08482669189565932</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.03316420104703968</v>
+        <v>0.09672731601102678</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.0551712126526865</v>
+        <v>-0.01496636747527096</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.05071571855858059</v>
+        <v>0.06902906317050309</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
@@ -7965,16 +7965,16 @@
         <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.3759742722037662</v>
+        <v>0.2600998482446124</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.01914177744079298</v>
+        <v>-0.03596167475866113</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.09262518626204748</v>
+        <v>-0.1210813579162695</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,16 +7992,16 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.006142377567785751</v>
+        <v>-0.009255497649392135</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.03183730670170884</v>
+        <v>0.0007326529704474172</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.05135140265027405</v>
+        <v>-0.01332743472288633</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -8010,31 +8010,31 @@
         <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.05467811713358755</v>
+        <v>-0.01288935888933821</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0454925134240363</v>
+        <v>0.0002766741090503657</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1177224106244065</v>
+        <v>0.06481382805165756</v>
       </c>
       <c r="BQ14" t="n">
         <v>-0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8046,19 +8046,19 @@
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.1960066316380888</v>
+        <v>0.1873305495140359</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.02166843389483894</v>
+        <v>-0.09163820734764255</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0337049356269357</v>
+        <v>-0.02455882335296199</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8067,25 +8067,25 @@
         <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.08066729636694167</v>
+        <v>-0.09423190516313289</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.008972519369115433</v>
+        <v>0.06362472377938948</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01535078414867847</v>
+        <v>0.01551393014464244</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ14" t="n">
         <v>-0</v>
@@ -8094,58 +8094,58 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.02215183954925417</v>
+        <v>-0.07794031967236188</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.06066607291819601</v>
+        <v>0.08953751782941237</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.09967332353897548</v>
+        <v>0.03781624145055152</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.07117243338240935</v>
+        <v>-0.09247519144274637</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.02248849534178899</v>
+        <v>0.06730108521059515</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01489478581314506</v>
+        <v>0.01442014679096143</v>
       </c>
       <c r="DA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB14" t="n">
         <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD14" t="n">
         <v>0</v>
@@ -8154,22 +8154,22 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.003741794435929306</v>
+        <v>0.003112174815130873</v>
       </c>
       <c r="DG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.01871409537674262</v>
+        <v>0.0150511781156988</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.03702391390006553</v>
+        <v>-0.03866478860418437</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
@@ -8181,151 +8181,151 @@
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.04885650802916838</v>
+        <v>-0.05791891649557802</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.01446766111850815</v>
+        <v>-0.01176024178873872</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.03316953437169993</v>
+        <v>-0.007207854064189963</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0438489188304958</v>
+        <v>0.08393436212077429</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.001149955514790745</v>
+        <v>0.03594064270488417</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.05687772426192475</v>
+        <v>-0.07454503663860224</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.06911683363151017</v>
+        <v>-0.0495870797112623</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.02299052186341357</v>
+        <v>0.05856435820876767</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.02988402928089696</v>
+        <v>0.01698095629039901</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
         <v>-0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.05176796436357432</v>
+        <v>-0.03986683437926694</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.03111458654780713</v>
+        <v>0.05452924840971168</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.007250029016247001</v>
+        <v>-0.02660631516206833</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW14" t="n">
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.07233281828392406</v>
+        <v>-0.0974779713734345</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.01625004158412825</v>
+        <v>0.07255416195614338</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.006410697439343241</v>
+        <v>-0.00166481132365308</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.009991464683040772</v>
+        <v>-0.02143477387932599</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0117035573966711</v>
+        <v>0.04062153230752507</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.03400145871863834</v>
+        <v>-0.03925011179581708</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
@@ -8337,28 +8337,28 @@
         <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.001742342230571659</v>
+        <v>0.00914928195777647</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.002632620354687212</v>
+        <v>0.08788678793494081</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.003404350071809533</v>
+        <v>-0.01157723687015044</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
         <v>0</v>
@@ -8367,31 +8367,31 @@
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.01634329917391489</v>
+        <v>-0.07796487328060303</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.03699785307823184</v>
+        <v>0.03672524783598674</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8399,22 +8399,22 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3860685444695524</v>
+        <v>0.3647806793238299</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1141690800741555</v>
+        <v>-0.172036741715225</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08271188432472305</v>
+        <v>0.01968429395090859</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
         <v>-0</v>
@@ -8426,22 +8426,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1829355616396811</v>
+        <v>0.2183298321620929</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.01446054530959619</v>
+        <v>-0.02217985210314379</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.04453142952883181</v>
+        <v>-0.002924705141801217</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8450,52 +8450,52 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1369772785662917</v>
+        <v>0.1016377250136189</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.02982205587082784</v>
+        <v>-0.02922826636402784</v>
       </c>
       <c r="W15" t="n">
-        <v>0.07347206322869854</v>
+        <v>-0.0691903113895815</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1260752604204138</v>
+        <v>-0.06636456577642461</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.04687873967860352</v>
+        <v>-0.173719828905508</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.03123882427387175</v>
+        <v>-0.0373524129183398</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
@@ -8504,19 +8504,19 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.0517373757069514</v>
+        <v>0.1479810468036685</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.04693577510272039</v>
+        <v>-0.07966742889036647</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.02873920170596778</v>
+        <v>0.1138387768089732</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
@@ -8534,16 +8534,16 @@
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.4352448661264277</v>
+        <v>0.3695804843578664</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.003029365963111259</v>
+        <v>-0.152308901954658</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.1354190088360794</v>
+        <v>-0.1137689097679482</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
@@ -8555,22 +8555,22 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.02836527991567364</v>
+        <v>-0.01617406426559779</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.03404178528994286</v>
+        <v>-0.02923407922887424</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1253338311084696</v>
+        <v>-0.02218312207148299</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -8579,7 +8579,7 @@
         <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,22 +8588,22 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.01864119223171074</v>
+        <v>-0.03116865778580338</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.04445658946713062</v>
+        <v>0.03884501496101608</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.05145281084716107</v>
+        <v>0.02711383900795365</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
@@ -8615,49 +8615,49 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2604690935085517</v>
+        <v>0.327082976889236</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0.02231307279963652</v>
+        <v>-0.1146176438750104</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.07943533834213067</v>
+        <v>-0.01424526978808908</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC15" t="n">
         <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.09827690266432829</v>
+        <v>-0.1396795763294643</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.02618285090985644</v>
+        <v>0.1470726399942006</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.02315152757546453</v>
+        <v>-0.04254836521647105</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
@@ -8669,19 +8669,19 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.05345134043065182</v>
+        <v>-0.1298057512778343</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.07476594241106028</v>
+        <v>0.2248686083792075</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.167076016087498</v>
+        <v>0.02927684884562921</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
@@ -8696,22 +8696,22 @@
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.09150580622032395</v>
+        <v>-0.1285504083555058</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.03576284586004064</v>
+        <v>0.1408212952413083</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.01998796279913451</v>
+        <v>-0.02884671728370796</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>-0</v>
@@ -8720,25 +8720,25 @@
         <v>0</v>
       </c>
       <c r="DE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.04256947303042163</v>
+        <v>-0.03811654224551935</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.01581421298383295</v>
+        <v>0.01736056773571083</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0004951969159955818</v>
+        <v>0.005380772385159763</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
@@ -8747,22 +8747,22 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.05204242744462474</v>
+        <v>-0.07924915251009387</v>
       </c>
       <c r="DP15" t="n">
         <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.005463698325473166</v>
+        <v>0.06638603440898624</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.06204460443714819</v>
+        <v>-0.01112876349694857</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
@@ -8777,76 +8777,76 @@
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.08895742217609767</v>
+        <v>-0.005933609110331424</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.0204191241031179</v>
+        <v>-0.09247220723306046</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.006132100995516686</v>
+        <v>0.1089573596793195</v>
       </c>
       <c r="EB15" t="n">
         <v>0</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
         <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.06172239568230441</v>
+        <v>-0.08750035412337751</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.03635916135260377</v>
+        <v>0.1098907892894518</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.03997454528862483</v>
+        <v>0.0115433616085429</v>
       </c>
       <c r="EK15" t="n">
         <v>-0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.07627387971790586</v>
+        <v>-0.08446253302355194</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.0206473654388265</v>
+        <v>0.06189068000717168</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.03062252082218282</v>
+        <v>-0.03677841590866018</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8855,25 +8855,25 @@
         <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.1025882726777533</v>
+        <v>-0.1546360374439853</v>
       </c>
       <c r="EZ15" t="n">
         <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.04450534965843048</v>
+        <v>0.161990290820082</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.02725858841128379</v>
+        <v>-0.05172216921175717</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
@@ -8885,16 +8885,16 @@
         <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.007373691659527414</v>
+        <v>-0.1230854776103581</v>
       </c>
       <c r="FI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.06288626401431556</v>
+        <v>0.09742313101848125</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.04604291415433229</v>
+        <v>-0.004779892956332153</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
@@ -8903,64 +8903,64 @@
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.01410257397447073</v>
+        <v>-0.01614694594528322</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0.1281988544453152</v>
+        <v>-0.168954940891126</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.02382377109969946</v>
+        <v>-0.02410282736933757</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.04158371759998803</v>
+        <v>-0.1131176495357851</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.04610191740933486</v>
+        <v>0.08896809644111335</v>
       </c>
       <c r="GC15" t="n">
         <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -9534,22 +9534,22 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1052658734163721</v>
+        <v>0.627422820536647</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.04320202057340328</v>
+        <v>0.06061191564797961</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.05905002278961895</v>
+        <v>-0.3559869063142942</v>
       </c>
       <c r="G17" t="n">
         <v>-0</v>
@@ -9564,7 +9564,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.04295118699287189</v>
+        <v>0.4848470099800309</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9573,13 +9573,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.02626478918343891</v>
+        <v>-0.07477875402112276</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.01779210163083662</v>
+        <v>-0.1248566387190366</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>-0</v>
@@ -9588,10 +9588,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.004315201574558581</v>
+        <v>0.1865836190134013</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -9600,16 +9600,16 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.02118477643181161</v>
+        <v>-0.1508150897546938</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02208182202543177</v>
+        <v>-0.054449992586172</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>-0</v>
@@ -9618,34 +9618,34 @@
         <v>-0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.02178893815435579</v>
+        <v>-0.02451221587952385</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.02255643972430705</v>
+        <v>-0.3043818300567229</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.008955529374286314</v>
+        <v>-0.08725303996372012</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01934415261992584</v>
+        <v>0.2047296173217211</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
@@ -9654,13 +9654,13 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01134245279903199</v>
+        <v>0.05375847318474691</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.02047164354368227</v>
+        <v>-0.18902297130363</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,22 +9669,22 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.08397229367139974</v>
+        <v>0.8549474041771488</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.03965968528460088</v>
+        <v>-0.2276815909294671</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.0307696123454659</v>
+        <v>-0.3443997222646378</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -9693,13 +9693,13 @@
         <v>-0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.03177258358605593</v>
+        <v>-0.06715582659037572</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,13 +9708,13 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.01930709527244431</v>
+        <v>-0.06485595659530104</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.01243948089378175</v>
+        <v>-0.06604753806436144</v>
       </c>
       <c r="BI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
         <v>-0</v>
@@ -9723,37 +9723,37 @@
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.04010860812152438</v>
+        <v>0.0822693464709838</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.02954463615503292</v>
+        <v>0.1436962341524636</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.01416156279207613</v>
+        <v>0.07772264146023329</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.04674285588966193</v>
+        <v>0.5563287333754479</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -9762,40 +9762,40 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.01788130102593049</v>
+        <v>-0.07118081701521775</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.002134030280392688</v>
+        <v>-0.2323851639056316</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
         <v>-0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.01621965963627819</v>
+        <v>-0.2479423257840932</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.005475792416234756</v>
+        <v>-0.02800688302190992</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.01726675697218584</v>
+        <v>0.1608544468760856</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
@@ -9807,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.005136498689521495</v>
+        <v>-0.3206695496005732</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,13 +9816,13 @@
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.002702375558682941</v>
+        <v>0.1436771340074288</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.02753638282070571</v>
+        <v>0.1762073625745528</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
         <v>0</v>
@@ -9831,25 +9831,25 @@
         <v>0</v>
       </c>
       <c r="CV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.0112676657924886</v>
+        <v>-0.2196143630494782</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.008010826526126556</v>
+        <v>-0.0466529040804157</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.022009830323133</v>
+        <v>0.1646349066419909</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
@@ -9858,76 +9858,76 @@
         <v>0</v>
       </c>
       <c r="DE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.004415211012725574</v>
+        <v>-0.04056075903832509</v>
       </c>
       <c r="DG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.02306287208739509</v>
+        <v>-0.2390961412322847</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.00406529454022137</v>
+        <v>0.005237428461781487</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.01511276425078155</v>
+        <v>-0.06403660509094541</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.0104815703175914</v>
+        <v>-0.05251297355714121</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.01640995735574316</v>
+        <v>0.02654311202393523</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.001985719039636225</v>
+        <v>0.1552989774217814</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
         <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.02253200220825065</v>
+        <v>-0.04428079943792719</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0.01452478347826923</v>
+        <v>0.05495848003892043</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
@@ -9939,10 +9939,10 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.009558445313801806</v>
+        <v>-0.0548734780467573</v>
       </c>
       <c r="EH17" t="n">
         <v>0</v>
@@ -9951,13 +9951,13 @@
         <v>0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.005821113327950961</v>
+        <v>-0.1350478032104411</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.01807824704006479</v>
+        <v>0.06551998943514274</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>0</v>
@@ -9966,52 +9966,52 @@
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.003430035122489143</v>
+        <v>-0.1124493129546077</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.01151076542301022</v>
+        <v>-0.1804588040648966</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.01703347142483065</v>
+        <v>0.1325432674203112</v>
       </c>
       <c r="EU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
         <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.007987245776195473</v>
+        <v>-0.2611165978457194</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.005474481293517712</v>
+        <v>-0.07421597977614532</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.02218428055851368</v>
+        <v>0.1393396736848286</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
@@ -10020,82 +10020,82 @@
         <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.0161118348492827</v>
+        <v>-0.2070471483929382</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.03139741915767542</v>
+        <v>0.08820371317209454</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.02060621513307019</v>
+        <v>0.2355773998782035</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.002414092888160417</v>
+        <v>-0.02774485721425285</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.00048274181441153</v>
+        <v>0.0007724081856934323</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.008386938207461912</v>
+        <v>0.1548384933794067</v>
       </c>
       <c r="FV17" t="n">
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.01601264112464079</v>
+        <v>-0.1212523038078352</v>
       </c>
       <c r="GA17" t="n">
         <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.01796211548304342</v>
+        <v>0.04147103644037487</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>0</v>
@@ -10103,28 +10103,28 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.08973733290996719</v>
+        <v>0.2077414505562488</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
         <v>-0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.04363036533815026</v>
+        <v>0.01466234705374211</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.02156490498913307</v>
+        <v>-0.1077644325869491</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -10133,34 +10133,34 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.03875571495573658</v>
+        <v>0.1794941332711215</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.03113179646541618</v>
+        <v>-0.02753071641080561</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.006479027623837866</v>
+        <v>-0.04495021081227519</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.006638853685983463</v>
+        <v>0.06180007958870848</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
@@ -10169,25 +10169,25 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.006616592756181581</v>
+        <v>-0.0558993875343902</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01804225124850013</v>
+        <v>-0.02169353517665368</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB18" t="n">
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.01810194689673993</v>
+        <v>-0.03144323551534938</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -10196,25 +10196,25 @@
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.02277404962828885</v>
+        <v>-0.1064793166329098</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.007477851005114849</v>
+        <v>-0.04613413275717124</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.01467252895541128</v>
+        <v>0.06097964293644918</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
@@ -10223,37 +10223,37 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.01457688889906194</v>
+        <v>0.01991828404009555</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.01261926141194078</v>
+        <v>-0.07216822196090436</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.07458258276590379</v>
+        <v>0.2432388761723343</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.02270858578158457</v>
+        <v>-0.1050297328403207</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.005921112505210411</v>
+        <v>-0.09223632430093449</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -10268,7 +10268,7 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.02902540495401127</v>
+        <v>-0.01399390515758598</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,37 +10277,37 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.02440380830372408</v>
+        <v>-0.02071822565696174</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.01810430359439813</v>
+        <v>-0.04481183372135537</v>
       </c>
       <c r="BI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
         <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.04438539492627638</v>
+        <v>0.02026315752943795</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.02128943147858666</v>
+        <v>0.0699021580394064</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.01175582963469083</v>
+        <v>0.05807575369095936</v>
       </c>
       <c r="BR18" t="n">
         <v>-0</v>
@@ -10316,13 +10316,13 @@
         <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.03760482512473504</v>
+        <v>0.1619083268834182</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -10331,16 +10331,16 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.009207733777462635</v>
+        <v>-0.03846608167488708</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.01177033560236127</v>
+        <v>-0.07636058453363764</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
         <v>-0</v>
@@ -10349,22 +10349,22 @@
         <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.01113963544823329</v>
+        <v>-0.06851210580353395</v>
       </c>
       <c r="CF18" t="n">
         <v>-0</v>
       </c>
       <c r="CG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.008540381151450074</v>
+        <v>0.002226543794065762</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.009504973902215511</v>
+        <v>0.06562853534023264</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>0</v>
@@ -10376,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.007565671789103549</v>
+        <v>-0.07212853004235267</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
@@ -10385,13 +10385,13 @@
         <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.00478063190907632</v>
+        <v>0.1004584927622055</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.01170301908861326</v>
+        <v>0.03650349465188414</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
         <v>-0</v>
@@ -10403,25 +10403,25 @@
         <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.006111028065611183</v>
+        <v>-0.06248877815009718</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.007956574682539366</v>
+        <v>-0.003929736350940091</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.01165319662273927</v>
+        <v>0.06837923266734859</v>
       </c>
       <c r="DB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD18" t="n">
         <v>0</v>
@@ -10430,19 +10430,19 @@
         <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.008646543992966443</v>
+        <v>-0.03093544367386237</v>
       </c>
       <c r="DG18" t="n">
         <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.000661436020803211</v>
+        <v>-0.01243639979336099</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.003792270102109945</v>
+        <v>-0.01681630782781365</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10451,31 +10451,31 @@
         <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.01474252436542887</v>
+        <v>-0.02629908806474939</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.01933505821069114</v>
+        <v>-0.01482057690703066</v>
       </c>
       <c r="DS18" t="n">
-        <v>-0.02131939216751958</v>
+        <v>-0.02146890654326647</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
         <v>-0</v>
@@ -10484,25 +10484,25 @@
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.0003051787991176317</v>
+        <v>0.03102927730278724</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.03126446484648008</v>
+        <v>-0.01044282629403498</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.02569133796986356</v>
+        <v>0.02663036916940175</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
       </c>
       <c r="ED18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE18" t="n">
         <v>-0</v>
@@ -10511,79 +10511,79 @@
         <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.004783702941119086</v>
+        <v>-0.02033096619267932</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.006898259031043298</v>
+        <v>-0.02586847692215741</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.0016330287825996</v>
+        <v>0.03588493470202741</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.004532262027226124</v>
+        <v>-0.0379261295103732</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.0005377438406086963</v>
+        <v>-0.02783907988881224</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.01839370892917774</v>
+        <v>0.04457929896783316</v>
       </c>
       <c r="EU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
         <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.004578271558871831</v>
+        <v>-0.07014806052570631</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.007737370836684438</v>
+        <v>-0.008723343313503471</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.01527916163317275</v>
+        <v>0.05111681997350929</v>
       </c>
       <c r="FD18" t="n">
         <v>0</v>
       </c>
       <c r="FE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF18" t="n">
         <v>-0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.007607065827906051</v>
+        <v>-0.062732692020456</v>
       </c>
       <c r="FI18" t="n">
         <v>0</v>
@@ -10601,67 +10601,67 @@
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.03354914501259099</v>
+        <v>0.02253889683855139</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.01303743320966156</v>
+        <v>0.04711148695033097</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.002179299737852478</v>
+        <v>-0.01556740577559344</v>
       </c>
       <c r="FR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS18" t="n">
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.000401249693616723</v>
+        <v>-0.0007360968758035229</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.003348842198980361</v>
+        <v>0.0483029259662929</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.02228688270709073</v>
+        <v>-0.04257255475824707</v>
       </c>
       <c r="GA18" t="n">
         <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.01637251541976336</v>
+        <v>0.04395152204113223</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
         <v>0</v>
@@ -11244,127 +11244,127 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3187051246916599</v>
+        <v>0.3551459068231119</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1489492520515811</v>
+        <v>-0.06624780114624799</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.09002751817248469</v>
+        <v>0.01098429745012845</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0622754085585477</v>
+        <v>-0.1016867037361101</v>
       </c>
       <c r="G20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>-0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1992021633405539</v>
+        <v>0.3409251365716396</v>
       </c>
       <c r="L20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1100223130379771</v>
+        <v>-0.1032063220192036</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.06384690876651669</v>
+        <v>-0.06126922043566328</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.03777947866233954</v>
+        <v>-0.03776431422260999</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.06748234503628472</v>
+        <v>0.04734494179420583</v>
       </c>
       <c r="U20" t="n">
         <v>-0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.01254594909241052</v>
+        <v>-0.08232009950528989</v>
       </c>
       <c r="W20" t="n">
-        <v>0.05182215268681091</v>
+        <v>-0.06073201395036021</v>
       </c>
       <c r="X20" t="n">
-        <v>0.04903665508515107</v>
+        <v>-0.03605285815306809</v>
       </c>
       <c r="Y20" t="n">
         <v>-0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.05591451940330632</v>
+        <v>-0.02133804096339007</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.04098066803660044</v>
+        <v>-0.1560318573565459</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.0113363782505748</v>
+        <v>-0.1148470254943638</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.01064786618755916</v>
+        <v>-0.04483845874131912</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.0004988108534246238</v>
+        <v>0.1068143413943105</v>
       </c>
       <c r="AM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>-0.02780742572324407</v>
+        <v>-0.05825390522548553</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.03672815432272445</v>
+        <v>0.05439081277967019</v>
       </c>
       <c r="AP20" t="n">
-        <v>-0.03421535914898376</v>
+        <v>-0.08972461437830465</v>
       </c>
       <c r="AQ20" t="n">
         <v>-0</v>
@@ -11373,25 +11373,25 @@
         <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.3203659829527116</v>
+        <v>0.3335868263825847</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>-0.0235898126052109</v>
+        <v>-0.009629259157114704</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.02984768583685589</v>
+        <v>-0.08780535925609508</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.02106020949174865</v>
+        <v>-0.09812328642952726</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
@@ -11403,103 +11403,103 @@
         <v>-0</v>
       </c>
       <c r="BC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>-0.001072429440116345</v>
+        <v>-0.01140236750930894</v>
       </c>
       <c r="BE20" t="n">
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>-0.02268530580535243</v>
+        <v>-0.06695445276446872</v>
       </c>
       <c r="BG20" t="n">
-        <v>-0.1044271899895412</v>
+        <v>-0.05139082285314105</v>
       </c>
       <c r="BH20" t="n">
-        <v>-0.0501200693083438</v>
+        <v>-0.0193104478582178</v>
       </c>
       <c r="BI20" t="n">
         <v>-0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL20" t="n">
         <v>-0</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.0592966882250069</v>
+        <v>0.02219673109581477</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.06457274857217001</v>
+        <v>0.002232439171185603</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.06362005606816112</v>
+        <v>0.08692222162543835</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.01862661953836153</v>
+        <v>0.01729389730064205</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU20" t="n">
         <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.152904167159655</v>
+        <v>0.2021413850493318</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>0.03566426065558426</v>
+        <v>-0.03783706356007563</v>
       </c>
       <c r="BY20" t="n">
-        <v>-0.009301953566094579</v>
+        <v>-0.02168645206373425</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.03284267381300353</v>
+        <v>-0.08911401918887189</v>
       </c>
       <c r="CA20" t="n">
         <v>-0</v>
       </c>
       <c r="CB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC20" t="n">
         <v>-0</v>
       </c>
       <c r="CD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE20" t="n">
-        <v>-0.061904795409631</v>
+        <v>-0.09791737837251817</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.01143126725340684</v>
+        <v>0.03225610680804188</v>
       </c>
       <c r="CH20" t="n">
-        <v>-0.004601576058983013</v>
+        <v>0.01974887851725612</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.03282588123079866</v>
+        <v>0.0362721956170256</v>
       </c>
       <c r="CJ20" t="n">
         <v>-0</v>
@@ -11508,28 +11508,28 @@
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN20" t="n">
-        <v>-0.02433470009147189</v>
+        <v>-0.1016975543828742</v>
       </c>
       <c r="CO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP20" t="n">
-        <v>-0.09528500233630727</v>
+        <v>0.08915633568965595</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.06538539023569021</v>
+        <v>0.1217066319068705</v>
       </c>
       <c r="CR20" t="n">
-        <v>-0.07160432678532314</v>
+        <v>0.08301250285341864</v>
       </c>
       <c r="CS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT20" t="n">
         <v>-0</v>
@@ -11538,22 +11538,22 @@
         <v>0</v>
       </c>
       <c r="CV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW20" t="n">
-        <v>-0.05000253652223097</v>
+        <v>-0.09174127876333839</v>
       </c>
       <c r="CX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY20" t="n">
-        <v>0.03351915909049587</v>
+        <v>0.02623950052228598</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-0.006271334416042406</v>
+        <v>0.01432238616037525</v>
       </c>
       <c r="DA20" t="n">
-        <v>0.04319125901262801</v>
+        <v>0.03659182256535285</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
@@ -11568,46 +11568,46 @@
         <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>-0.001289946644931425</v>
+        <v>-0.02671024991865038</v>
       </c>
       <c r="DG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.0591172678738161</v>
+        <v>-0.04319015153530167</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.004797224275910277</v>
+        <v>0.1105160589223386</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.005229672910767832</v>
+        <v>-0.009201923717437098</v>
       </c>
       <c r="DK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN20" t="n">
         <v>-0</v>
       </c>
       <c r="DO20" t="n">
-        <v>-0.0254965042945452</v>
+        <v>-0.08322142236751776</v>
       </c>
       <c r="DP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ20" t="n">
-        <v>0.05324006702549526</v>
+        <v>0.03760436146061279</v>
       </c>
       <c r="DR20" t="n">
-        <v>0.003712847301586662</v>
+        <v>-0.007618156034576174</v>
       </c>
       <c r="DS20" t="n">
-        <v>-0.008459506739143901</v>
+        <v>0.005632129299275784</v>
       </c>
       <c r="DT20" t="n">
         <v>0</v>
@@ -11616,196 +11616,196 @@
         <v>-0</v>
       </c>
       <c r="DV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX20" t="n">
-        <v>0.01337753817993134</v>
+        <v>0.06467366230099063</v>
       </c>
       <c r="DY20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ20" t="n">
-        <v>0.004357915243516064</v>
+        <v>0.008505927472670033</v>
       </c>
       <c r="EA20" t="n">
-        <v>-0.05459072035472773</v>
+        <v>-0.00783106266820404</v>
       </c>
       <c r="EB20" t="n">
-        <v>0.007400929234524437</v>
+        <v>0.02133215047088441</v>
       </c>
       <c r="EC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED20" t="n">
         <v>0</v>
       </c>
       <c r="EE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG20" t="n">
-        <v>-0.08162364597873287</v>
+        <v>-0.05904384290557171</v>
       </c>
       <c r="EH20" t="n">
         <v>-0</v>
       </c>
       <c r="EI20" t="n">
-        <v>0.05743983815859426</v>
+        <v>0.04834120355707774</v>
       </c>
       <c r="EJ20" t="n">
-        <v>0.04949568264106391</v>
+        <v>0.02638423161580142</v>
       </c>
       <c r="EK20" t="n">
-        <v>0.006716332308729729</v>
+        <v>-0.001698439665190165</v>
       </c>
       <c r="EL20" t="n">
         <v>-0</v>
       </c>
       <c r="EM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP20" t="n">
-        <v>-0.03908186418205387</v>
+        <v>-0.02245930463353922</v>
       </c>
       <c r="EQ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER20" t="n">
-        <v>0.003316639717130403</v>
+        <v>0.01060469725224102</v>
       </c>
       <c r="ES20" t="n">
-        <v>-0.02262352136749712</v>
+        <v>0.006178462308005487</v>
       </c>
       <c r="ET20" t="n">
-        <v>0.06565069416797123</v>
+        <v>0.08030112938705838</v>
       </c>
       <c r="EU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV20" t="n">
         <v>0</v>
       </c>
       <c r="EW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY20" t="n">
-        <v>-0.04613182958976267</v>
+        <v>-0.1071331813787448</v>
       </c>
       <c r="EZ20" t="n">
         <v>-0</v>
       </c>
       <c r="FA20" t="n">
-        <v>0.0176625289103931</v>
+        <v>0.0227492879967365</v>
       </c>
       <c r="FB20" t="n">
-        <v>0.006520506445012923</v>
+        <v>0.0106235942148288</v>
       </c>
       <c r="FC20" t="n">
-        <v>0.03459328209596833</v>
+        <v>0.02900336782100998</v>
       </c>
       <c r="FD20" t="n">
         <v>0</v>
       </c>
       <c r="FE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG20" t="n">
         <v>0</v>
       </c>
       <c r="FH20" t="n">
-        <v>0.03965977904545533</v>
+        <v>-0.03317414728052074</v>
       </c>
       <c r="FI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ20" t="n">
-        <v>0.05704261889428647</v>
+        <v>0.03266659876532933</v>
       </c>
       <c r="FK20" t="n">
-        <v>-0.00603480969582025</v>
+        <v>0.003943278395733587</v>
       </c>
       <c r="FL20" t="n">
-        <v>-0.002910244989505028</v>
+        <v>0.02763113854297916</v>
       </c>
       <c r="FM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO20" t="n">
         <v>0</v>
       </c>
       <c r="FP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>0.01095635583721517</v>
+        <v>-0.09027110150367833</v>
       </c>
       <c r="FR20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS20" t="n">
-        <v>0.01201145400328422</v>
+        <v>0.16897490766619</v>
       </c>
       <c r="FT20" t="n">
-        <v>0.006632200171119691</v>
+        <v>-0.009100134241440631</v>
       </c>
       <c r="FU20" t="n">
-        <v>0.01082056739895922</v>
+        <v>0.1117377186749091</v>
       </c>
       <c r="FV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>-0.006014361215978115</v>
+        <v>-0.09272021558676033</v>
       </c>
       <c r="GA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB20" t="n">
-        <v>-0.04180194767149894</v>
+        <v>-0.07432465772898592</v>
       </c>
       <c r="GC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD20" t="n">
-        <v>-0.01483391711139229</v>
+        <v>0.0006097985196584007</v>
       </c>
       <c r="GE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -12382,7 +12382,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1507833027504652</v>
+        <v>0.5180481033177419</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -12391,10 +12391,10 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.07467417371888677</v>
+        <v>0.06147994282379924</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.06653412378738222</v>
+        <v>-0.209093573008236</v>
       </c>
       <c r="G22" t="n">
         <v>-0</v>
@@ -12409,7 +12409,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1094409410262945</v>
+        <v>0.643979264321317</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -12418,13 +12418,13 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.05496168156868961</v>
+        <v>-0.07181431967098559</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.03744628605783663</v>
+        <v>-0.1110065846545526</v>
       </c>
       <c r="P22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>-0</v>
@@ -12433,10 +12433,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.01463975394307872</v>
+        <v>0.0825688503498333</v>
       </c>
       <c r="U22" t="n">
         <v>-0</v>
@@ -12445,25 +12445,25 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.02316929884272893</v>
+        <v>-0.06198560141531508</v>
       </c>
       <c r="X22" t="n">
-        <v>0.01937607019138276</v>
+        <v>0.04076128392298476</v>
       </c>
       <c r="Y22" t="n">
         <v>-0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.02767508389773804</v>
+        <v>0.01791058539452526</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -12472,13 +12472,13 @@
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.02618960847411302</v>
+        <v>-0.1630568678752857</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.001143404702909475</v>
+        <v>-0.07516107783948249</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>-0</v>
@@ -12490,61 +12490,61 @@
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.02473386421884555</v>
+        <v>0.07902847171312587</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>-0.01232726247392478</v>
+        <v>0.0130707113805475</v>
       </c>
       <c r="AP22" t="n">
-        <v>-0.03229264730419328</v>
+        <v>-0.1534995418770378</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR22" t="n">
         <v>-0</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.09588355770063949</v>
+        <v>0.4745401595134287</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW22" t="n">
         <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>-0.0324299892848357</v>
+        <v>-0.223957936144948</v>
       </c>
       <c r="AY22" t="n">
-        <v>-0.03545442588276625</v>
+        <v>-0.1342807609504265</v>
       </c>
       <c r="AZ22" t="n">
         <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC22" t="n">
         <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>0.02983601455468899</v>
+        <v>0.006898298446222749</v>
       </c>
       <c r="BE22" t="n">
         <v>0</v>
@@ -12553,52 +12553,52 @@
         <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>-0.04119053948865173</v>
+        <v>-0.05945762377877578</v>
       </c>
       <c r="BH22" t="n">
-        <v>-0.005366368448716368</v>
+        <v>-0.1059214426079688</v>
       </c>
       <c r="BI22" t="n">
         <v>-0</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL22" t="n">
         <v>-0</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.04251893030799123</v>
+        <v>0.0813423821057223</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP22" t="n">
-        <v>0.02635054973591057</v>
+        <v>0.09997891046611389</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0.01899540148185775</v>
+        <v>-0.001708946803609338</v>
       </c>
       <c r="BR22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS22" t="n">
         <v>0</v>
       </c>
       <c r="BT22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV22" t="n">
-        <v>0.05881871221633909</v>
+        <v>0.2973278672917199</v>
       </c>
       <c r="BW22" t="n">
         <v>0</v>
@@ -12607,37 +12607,37 @@
         <v>0</v>
       </c>
       <c r="BY22" t="n">
-        <v>-0.02185609697105313</v>
+        <v>-0.08465652771461853</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.005844403953537277</v>
+        <v>-0.08813786074675257</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC22" t="n">
         <v>-0</v>
       </c>
       <c r="CD22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE22" t="n">
-        <v>-0.0190709811779678</v>
+        <v>-0.1509462880393314</v>
       </c>
       <c r="CF22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG22" t="n">
         <v>-0</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.007675109732017718</v>
+        <v>0.03739010556203573</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.01547887986884864</v>
+        <v>0.06568594532480369</v>
       </c>
       <c r="CJ22" t="n">
         <v>-0</v>
@@ -12646,13 +12646,13 @@
         <v>0</v>
       </c>
       <c r="CL22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM22" t="n">
         <v>0</v>
       </c>
       <c r="CN22" t="n">
-        <v>0.001084650870710764</v>
+        <v>-0.2408495160815819</v>
       </c>
       <c r="CO22" t="n">
         <v>-0</v>
@@ -12661,13 +12661,13 @@
         <v>-0</v>
       </c>
       <c r="CQ22" t="n">
-        <v>-0.01264115901661678</v>
+        <v>0.2585020257848481</v>
       </c>
       <c r="CR22" t="n">
-        <v>-0.02859485132024796</v>
+        <v>0.1242683961836985</v>
       </c>
       <c r="CS22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT22" t="n">
         <v>-0</v>
@@ -12679,19 +12679,19 @@
         <v>-0</v>
       </c>
       <c r="CW22" t="n">
-        <v>-0.01511049122574344</v>
+        <v>-0.1537191133321979</v>
       </c>
       <c r="CX22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY22" t="n">
         <v>0</v>
       </c>
       <c r="CZ22" t="n">
-        <v>0.005730089539273469</v>
+        <v>-0.005172126432719299</v>
       </c>
       <c r="DA22" t="n">
-        <v>0.02210293220111836</v>
+        <v>0.05930396982316762</v>
       </c>
       <c r="DB22" t="n">
         <v>0</v>
@@ -12706,19 +12706,19 @@
         <v>0</v>
       </c>
       <c r="DF22" t="n">
-        <v>0.001469904406129279</v>
+        <v>0.002126596608247948</v>
       </c>
       <c r="DG22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI22" t="n">
-        <v>0.01673648575857769</v>
+        <v>-0.0605692745775366</v>
       </c>
       <c r="DJ22" t="n">
-        <v>0.001094121716201831</v>
+        <v>0.01037031573494669</v>
       </c>
       <c r="DK22" t="n">
         <v>0</v>
@@ -12730,22 +12730,22 @@
         <v>0</v>
       </c>
       <c r="DN22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO22" t="n">
-        <v>-0.01826452097067918</v>
+        <v>-0.08112097273615204</v>
       </c>
       <c r="DP22" t="n">
         <v>-0</v>
       </c>
       <c r="DQ22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR22" t="n">
-        <v>0.02629721780048799</v>
+        <v>-0.03961490702160498</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.0307774575120966</v>
+        <v>-0.005410691007561073</v>
       </c>
       <c r="DT22" t="n">
         <v>-0</v>
@@ -12754,25 +12754,25 @@
         <v>-0</v>
       </c>
       <c r="DV22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW22" t="n">
         <v>-0</v>
       </c>
       <c r="DX22" t="n">
-        <v>0.0001847505999447847</v>
+        <v>0.05379098968229609</v>
       </c>
       <c r="DY22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ22" t="n">
         <v>0</v>
       </c>
       <c r="EA22" t="n">
-        <v>-0.02619775491746928</v>
+        <v>-0.05268054833391958</v>
       </c>
       <c r="EB22" t="n">
-        <v>-0.01772487370828326</v>
+        <v>-0.05592312843756012</v>
       </c>
       <c r="EC22" t="n">
         <v>-0</v>
@@ -12787,76 +12787,76 @@
         <v>0</v>
       </c>
       <c r="EG22" t="n">
-        <v>-0.01085945387854833</v>
+        <v>-0.03698881960208775</v>
       </c>
       <c r="EH22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ22" t="n">
-        <v>0.01774826038541308</v>
+        <v>-0.05929001476202606</v>
       </c>
       <c r="EK22" t="n">
-        <v>0.002849313117947491</v>
+        <v>0.02433424203969798</v>
       </c>
       <c r="EL22" t="n">
         <v>-0</v>
       </c>
       <c r="EM22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP22" t="n">
-        <v>-0.004220568307922598</v>
+        <v>-0.0693866785405625</v>
       </c>
       <c r="EQ22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES22" t="n">
-        <v>-0.01063190175657089</v>
+        <v>-0.03800474644069021</v>
       </c>
       <c r="ET22" t="n">
-        <v>-0.02310275477909809</v>
+        <v>-0.09810446638067608</v>
       </c>
       <c r="EU22" t="n">
         <v>-0</v>
       </c>
       <c r="EV22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY22" t="n">
-        <v>-0.01192516502674933</v>
+        <v>-0.163350001726733</v>
       </c>
       <c r="EZ22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA22" t="n">
         <v>-0</v>
       </c>
       <c r="FB22" t="n">
-        <v>0.003181824698183061</v>
+        <v>0.007860646053425525</v>
       </c>
       <c r="FC22" t="n">
-        <v>0.0222865266786864</v>
+        <v>0.05230941185838079</v>
       </c>
       <c r="FD22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE22" t="n">
         <v>0</v>
@@ -12865,37 +12865,37 @@
         <v>-0</v>
       </c>
       <c r="FG22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH22" t="n">
-        <v>-0.01230257420660831</v>
+        <v>-0.1325234891259381</v>
       </c>
       <c r="FI22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ22" t="n">
         <v>-0</v>
       </c>
       <c r="FK22" t="n">
-        <v>-0.0402899169604589</v>
+        <v>0.07938080095738352</v>
       </c>
       <c r="FL22" t="n">
-        <v>0.01520103024520643</v>
+        <v>0.1221670086556265</v>
       </c>
       <c r="FM22" t="n">
         <v>0</v>
       </c>
       <c r="FN22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO22" t="n">
         <v>0</v>
       </c>
       <c r="FP22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ22" t="n">
-        <v>-0.002409298342595829</v>
+        <v>-0.1169374370399837</v>
       </c>
       <c r="FR22" t="n">
         <v>-0</v>
@@ -12904,37 +12904,37 @@
         <v>-0</v>
       </c>
       <c r="FT22" t="n">
-        <v>-0.0003948844006530285</v>
+        <v>0.01811202582686371</v>
       </c>
       <c r="FU22" t="n">
-        <v>0.01479161714737616</v>
+        <v>0.07554990158658766</v>
       </c>
       <c r="FV22" t="n">
         <v>-0</v>
       </c>
       <c r="FW22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ22" t="n">
-        <v>-0.01431095049276781</v>
+        <v>-0.07945850591444292</v>
       </c>
       <c r="GA22" t="n">
         <v>0</v>
       </c>
       <c r="GB22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD22" t="n">
-        <v>-0.0228038178607163</v>
+        <v>-0.04679376899199307</v>
       </c>
       <c r="GE22" t="n">
         <v>-0</v>
